--- a/case_studies/backbone/technologies.xlsx
+++ b/case_studies/backbone/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAF5521-5B36-4A63-A4EA-EDE4F05259CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD2C54C-403D-4BD3-9890-AEA9B5C13438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -440,9 +440,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -519,7 +519,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1066,9 +1066,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
   <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>

--- a/case_studies/backbone/technologies.xlsx
+++ b/case_studies/backbone/technologies.xlsx
@@ -1,25 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD2C54C-403D-4BD3-9890-AEA9B5C13438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A6431C-3712-4B36-A5BF-1B5DFB9BEE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
     <sheet name="new" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -527,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -557,10 +568,10 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>946.41</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>946.41</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -607,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>45.67</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -684,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -711,16 +722,16 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>515.12</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>515.12</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>38.840000000000003</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -755,13 +766,13 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -865,10 +876,10 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -951,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1019,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="O8">
         <v>0</v>

--- a/case_studies/backbone/technologies.xlsx
+++ b/case_studies/backbone/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A6431C-3712-4B36-A5BF-1B5DFB9BEE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7D2231-425C-4586-A120-04EC10B4000F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28935" yWindow="-375" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="J7">
         <v>0</v>

--- a/case_studies/backbone/technologies.xlsx
+++ b/case_studies/backbone/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7D2231-425C-4586-A120-04EC10B4000F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046986E5-D3D1-4AA3-8B60-278B628CEAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-375" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -633,13 +633,13 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -710,13 +710,14 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>18.3</v>
+        <f>18.4+14.4</f>
+        <v>32.799999999999997</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -766,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -787,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>163.6</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -947,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1030,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>329</v>
+        <v>654</v>
       </c>
       <c r="N8">
-        <v>329</v>
+        <v>654</v>
       </c>
       <c r="O8">
         <v>0</v>

--- a/case_studies/backbone/technologies.xlsx
+++ b/case_studies/backbone/technologies.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046986E5-D3D1-4AA3-8B60-278B628CEAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9D4201-B1FB-4269-B44E-7684C78B1B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="existing" sheetId="1" r:id="rId1"/>
+    <sheet name="existing" sheetId="3" r:id="rId1"/>
     <sheet name="new" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -449,7 +449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32646D9-68BB-474D-B725-BABE5F54D2FA}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -559,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -568,10 +568,10 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>946.41</v>
+        <v>947</v>
       </c>
       <c r="N2">
-        <v>946.41</v>
+        <v>947</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>45.67</v>
+        <v>46</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -627,19 +627,19 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>16.5</v>
+        <v>37</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K3">
-        <v>34.700000000000003</v>
+        <v>78</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>39.950000000000003</v>
+        <v>40</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -704,35 +704,34 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <f>18.4+14.4</f>
-        <v>32.799999999999997</v>
+        <v>50</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K4">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>515.12</v>
+        <v>516</v>
       </c>
       <c r="N4">
-        <v>515.12</v>
+        <v>516</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>38.840000000000003</v>
+        <v>32</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -744,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -782,19 +781,19 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="K5">
-        <v>163.6</v>
+        <v>78</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -821,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -868,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -942,13 +941,13 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>55.6</v>
+        <v>46</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K7">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -963,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -975,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -1022,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1162,76 +1161,76 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -1239,76 +1238,76 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
@@ -1316,76 +1315,76 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -1393,76 +1392,76 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -1470,76 +1469,76 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -1547,76 +1546,76 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -1624,76 +1623,76 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/case_studies/backbone/technologies.xlsx
+++ b/case_studies/backbone/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9D4201-B1FB-4269-B44E-7684C78B1B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35507845-8D04-4247-AED7-62E135D8B6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -793,7 +793,7 @@
         <v>71</v>
       </c>
       <c r="K5">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1161,76 +1161,76 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -1238,76 +1238,76 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
@@ -1315,76 +1315,76 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -1392,76 +1392,76 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -1469,76 +1469,76 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -1546,76 +1546,76 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -1623,76 +1623,76 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/case_studies/backbone/technologies.xlsx
+++ b/case_studies/backbone/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35507845-8D04-4247-AED7-62E135D8B6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1CFF25-B6AF-430F-9DB4-93DF06FB1E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
